--- a/data/demo/Tecnolink-Traffic-2026-08-12~2026-08-12.xlsx
+++ b/data/demo/Tecnolink-Traffic-2026-08-12~2026-08-12.xlsx
@@ -83,7 +83,7 @@
     <t>608620402034373</t>
   </si>
   <si>
-    <t>Crystal Ceiling Fan with Light, E27 Base Low Profile Fan Ceiling Lamp, 3-Color Stepless Dimming, 3-Speed Wind, Silent Fan Light with Remote Control, 2 Installation Methods for Bedroom, Living Room, Kitchen &amp; Dining Room</t>
+    <t>Round Crystal Ceiling Fan with Light, E27 Screw-in Low Profile Fan Ceiling Lamp, 3-Color Stepless Dimming, 3 Adjustable Wind Speeds, Quiet Fan Light with Remote Control, Decorative Lighting for Breakfast Nook, Dining Space &amp; Lobby</t>
   </si>
   <si>
     <t>3319</t>
@@ -368,7 +368,7 @@
     <t>608127822967446</t>
   </si>
   <si>
-    <t>TIANLAI Foco LED Recargable Portátil, Lámpara de Emergencia 15W (Equivalente 75W), 120 Lúmenes, Carga Tipo-C Bajo Voltaje 5V, 3 Modos de Luz Alta/Baja/SOS, Lampara Colgante para Campamento, Cortes de Luz, Pesca y Puestos</t>
+    <t>TIANLAI Foco LED Recargable Portátil, Lámpara de Emergencia 15W/24W/36W, Carga Tipo-C Bajo Voltaje 5V, 3 Modos de Luz Alta/Baja/SOS, Lampara Colgante para Campamento, Cortes de Luz, Pesca y Puestos</t>
   </si>
   <si>
     <t>2224</t>
@@ -503,7 +503,7 @@
     <t>605123275288511</t>
   </si>
   <si>
-    <t>Altavoz de Karaoke Portátil Bluetooth, Máquina de karaoke con micrófono inalámbrico, Efectos de Luz RGB, karaoke portátil para reuniones, fiestas, regalo de Navidad, máquina de karaoke portátil para adultos/micrófono de karaoke con luces LED, altavoz de karaoke compatible con tarjeta TF/USB</t>
+    <t>Altavoz de Karaoke Portátil Bluetooth, Máquina de karaoke con micrófono inalámbrico, carcasa de plástico ABS, Efectos de Luz RGB, karaoke portátil para reuniones, fiestas, regalo de Navidad, máquina de karaoke portátil para adultos/micrófono de karaoke con luces LED, altavoz de karaoke compatible con tarjeta TF/USB</t>
   </si>
   <si>
     <t>400</t>
@@ -680,7 +680,7 @@
     <t>608671941654784</t>
   </si>
   <si>
-    <t>KBroad BT Speaker with 1 Free Wireless Microphone, Altavoces Dobles 3 Pulgadas 10W Alta Potencia, Sonido HiFi Karaoke, Bluetooth + TWS, Luces RGB, Batería 1800mAh Recargable, Carga Tipo-C, Reproducción Bluetooth/USB/FM. Ideal para Karaoke, Fiestas, Hogar y Actividades al Aire Libre</t>
+    <t>KBroad BT Speaker with 1 Free Wireless Microphone, Altavoces Dobles 3 Pulgadas 20W Alta Potencia, Sonido HiFi Karaoke, Bluetooth + TWS, Luces RGB, Batería 1800mAh Recargable, Carga Tipo-C, Reproducción Bluetooth/USB/FM. Ideal para Karaoke, Fiestas, Hogar y Actividades al Aire Libre</t>
   </si>
   <si>
     <t>595</t>
